--- a/_experimentalData/e4WatchData/E4_data_baseline_featureAnalysis_3_axis_acceleration_feature.xlsx
+++ b/_experimentalData/e4WatchData/E4_data_baseline_featureAnalysis_3_axis_acceleration_feature.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1038727246256983</v>
+        <v>0.2023009232018542</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00192976047055329</v>
+        <v>0.003015250735239517</v>
       </c>
     </row>
   </sheetData>
